--- a/tests/downloads/Provider_All_Bookings.xlsx
+++ b/tests/downloads/Provider_All_Bookings.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,10 +433,10 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="str">
-        <v>FTB000096</v>
+        <v>FTB000109</v>
       </c>
       <c r="F2">
         <v>8260</v>
@@ -445,10 +445,10 @@
         <v>pending</v>
       </c>
       <c r="H2" t="str">
-        <v>4/7/2026, 11:47:16 AM</v>
+        <v>5/4/2026, 4:11:57 PM</v>
       </c>
       <c r="I2" t="str">
-        <v>4/7/2026, 5:17:16 PM</v>
+        <v>5/4/2026, 9:41:57 PM</v>
       </c>
       <c r="J2" t="str">
         <v>processing</v>
@@ -456,10 +456,10 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="str">
-        <v>FTB000089</v>
+        <v>FTB000096</v>
       </c>
       <c r="F3">
         <v>8260</v>
@@ -468,10 +468,10 @@
         <v>pending</v>
       </c>
       <c r="H3" t="str">
-        <v>3/30/2026, 11:35:02 AM</v>
+        <v>4/7/2026, 11:47:16 AM</v>
       </c>
       <c r="I3" t="str">
-        <v>3/30/2026, 5:05:02 PM</v>
+        <v>4/7/2026, 5:17:16 PM</v>
       </c>
       <c r="J3" t="str">
         <v>processing</v>
@@ -479,10 +479,10 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>FTB000051</v>
+        <v>FTB000089</v>
       </c>
       <c r="F4">
         <v>8260</v>
@@ -491,10 +491,10 @@
         <v>pending</v>
       </c>
       <c r="H4" t="str">
-        <v>3/6/2026, 6:11:50 PM</v>
+        <v>3/30/2026, 11:35:02 AM</v>
       </c>
       <c r="I4" t="str">
-        <v>3/6/2026, 11:41:50 PM</v>
+        <v>3/30/2026, 5:05:02 PM</v>
       </c>
       <c r="J4" t="str">
         <v>processing</v>
@@ -502,30 +502,53 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>FTB000022</v>
+        <v>FTB000051</v>
       </c>
       <c r="F5">
         <v>8260</v>
       </c>
       <c r="G5" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H5" t="str">
+        <v>3/6/2026, 6:11:50 PM</v>
+      </c>
+      <c r="I5" t="str">
+        <v>3/6/2026, 11:41:50 PM</v>
+      </c>
+      <c r="J5" t="str">
+        <v>processing</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="str">
+        <v>FTB000022</v>
+      </c>
+      <c r="F6">
+        <v>8260</v>
+      </c>
+      <c r="G6" t="str">
         <v>paid</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H6" t="str">
         <v>2/12/2026, 5:03:42 PM</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I6" t="str">
         <v>2/12/2026, 9:20:17 PM</v>
       </c>
-      <c r="J5" t="str">
+      <c r="J6" t="str">
         <v>processing</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J6"/>
   </ignoredErrors>
 </worksheet>
 </file>